--- a/tests/Functional/Batch/files/validated.xlsx
+++ b/tests/Functional/Batch/files/validated.xlsx
@@ -49,7 +49,7 @@
     <t>test</t>
   </si>
   <si>
-    <t>sourin.sutradhar@gmail.com</t>
+    <t>mhobbes09@gmail.com</t>
   </si>
   <si>
     <t>test payment link</t>
@@ -90,13 +90,10 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
-    <font>
-      <sz val="10.0"/>
-    </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -184,7 +181,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="2">
-        <v>7.829459269E9</v>
+        <v>7.0E9</v>
       </c>
       <c r="E2" s="2">
         <v>100.0</v>
@@ -208,7 +205,7 @@
         <v>12</v>
       </c>
       <c r="D3" s="2">
-        <v>7.829459269E9</v>
+        <v>7.0E9</v>
       </c>
       <c r="E3" s="2">
         <v>1.0</v>
@@ -238,7 +235,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="2">
-        <v>7.829459269E9</v>
+        <v>7.0E9</v>
       </c>
       <c r="E4" s="2">
         <v>200.0</v>
